--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486956_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486956_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.113</v>
+        <v>9.379</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8848</v>
+        <v>7.1211</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2282</v>
+        <v>2.2579</v>
       </c>
       <c r="G2" t="n">
         <v>8.577</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.848</v>
+        <v>-0.582</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2907</v>
+        <v>-0.0544</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5572</v>
+        <v>-0.5276</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8412</v>
+        <v>4.3807</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0684</v>
+        <v>4.1928</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2271</v>
+        <v>0.1879</v>
       </c>
       <c r="G3" t="n">
         <v>4.8251</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3734</v>
+        <v>-0.0871</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4992</v>
+        <v>0.6237</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1258</v>
+        <v>-0.7108</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5095</v>
+        <v>2.7403</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8902</v>
+        <v>2.3285</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6193</v>
+        <v>0.4118</v>
       </c>
       <c r="G4" t="n">
         <v>3.5234</v>
@@ -766,13 +766,13 @@
         <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7335</v>
+        <v>-0.0358</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.2401</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0684</v>
+        <v>-0.2759</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1314</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4722</v>
+        <v>2.627</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8651</v>
+        <v>0.931</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6071</v>
+        <v>1.696</v>
       </c>
       <c r="G5" t="n">
         <v>1.2777</v>
@@ -844,13 +844,13 @@
         <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0642</v>
+        <v>-0.9094</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7246</v>
+        <v>-0.6587</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3396</v>
+        <v>-0.2507</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6424</v>
+        <v>1.7972</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0212</v>
+        <v>1.0871</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6212</v>
+        <v>0.7101</v>
       </c>
       <c r="G6" t="n">
         <v>0.3851</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8434</v>
+        <v>-0.6886</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.527</v>
+        <v>-0.4611</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3164</v>
+        <v>-0.2275</v>
       </c>
       <c r="V6" t="n">
         <v>0.4579</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9645</v>
+        <v>1.4785</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1953</v>
+        <v>-0.711</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1599</v>
+        <v>2.1895</v>
       </c>
       <c r="G7" t="n">
         <v>1.983</v>
@@ -1000,13 +1000,13 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2587</v>
+        <v>-0.7447</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7905</v>
+        <v>-0.3062</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4682</v>
+        <v>-0.4385</v>
       </c>
       <c r="V7" t="n">
         <v>0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6494</v>
+        <v>0.7087</v>
       </c>
       <c r="E8" t="n">
         <v>1.6223</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9729</v>
+        <v>-0.9136</v>
       </c>
       <c r="G8" t="n">
         <v>1.7149</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2976</v>
+        <v>-0.2383</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0341</v>
+        <v>0.0252</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3884</v>
+        <v>0.6081</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2428</v>
+        <v>-0.4835</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8544</v>
+        <v>1.0916</v>
       </c>
       <c r="G9" t="n">
         <v>0.5615</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7713</v>
+        <v>-0.7748</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9222</v>
+        <v>-0.1628</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8491</v>
+        <v>-0.612</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5589</v>
+        <v>-0.2542</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1364</v>
+        <v>0.4115</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6953</v>
+        <v>-0.6657</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6997</v>
@@ -1234,13 +1234,13 @@
         <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0379</v>
+        <v>-0.7331</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>-0.3836</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3791</v>
+        <v>-0.3495</v>
       </c>
       <c r="V10" t="n">
         <v>1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6812</v>
+        <v>-1.2426</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8244</v>
+        <v>-2.6152</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1432</v>
+        <v>1.3725</v>
       </c>
       <c r="G11" t="n">
         <v>1.4131</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6101</v>
+        <v>0.0486</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.527</v>
+        <v>-0.3178</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1371</v>
+        <v>0.3664</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.5637</v>
+        <v>22.2227</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2259</v>
+        <v>13.8846</v>
       </c>
       <c r="F12" t="n">
-        <v>8.338000000000001</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>23.5611</v>
@@ -1390,13 +1390,13 @@
         <v>16.4275</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.404100000000001</v>
+        <v>-4.745200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4031</v>
+        <v>-1.7443</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0008</v>
+        <v>-3.0009</v>
       </c>
       <c r="V12" t="n">
         <v>0.3265</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6268</v>
+        <v>4.91</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0625</v>
+        <v>6.1085</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4357</v>
+        <v>-1.1985</v>
       </c>
       <c r="G13" t="n">
         <v>2.437</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5351</v>
+        <v>-0.2519</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1857</v>
+        <v>-0.1397</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3494</v>
+        <v>-0.1122</v>
       </c>
       <c r="V13" t="n">
         <v>1.2875</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>M. BETCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4041</v>
+        <v>-0.6879</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3197</v>
+        <v>-0.0232</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9156</v>
+        <v>-0.6647</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.431</v>
+        <v>-1.2613</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6574</v>
+        <v>0.3016</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7736</v>
+        <v>-1.5629</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2797</v>
+        <v>0.004</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2862</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5659</v>
+        <v>-0.6579</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1513</v>
+        <v>-1.2653</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9436</v>
+        <v>-0.3602</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2077</v>
+        <v>-0.905</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1924</v>
+        <v>0.3681</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5646</v>
+        <v>-0.0271</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6278</v>
+        <v>0.3952</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2999</v>
+        <v>-1.2521</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4631</v>
+        <v>0.9599</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1632</v>
+        <v>-2.212</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.2292</v>
+        <v>-2.431</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.9479</v>
+        <v>-1.6574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2813</v>
+        <v>-0.7736</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9308</v>
+        <v>-0.2797</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.0886</v>
+        <v>0.2862</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1579</v>
+        <v>-0.5659</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2984</v>
+        <v>-2.1513</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8593</v>
+        <v>-1.9436</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4391</v>
+        <v>-0.2077</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0772</v>
+        <v>1.5361</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6691</v>
+        <v>1.2047</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4082</v>
+        <v>0.3314</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8521</v>
+        <v>-1.1786</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8521</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BETCH</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7925</v>
+        <v>-1.3827</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1278</v>
+        <v>-0.8919</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6647</v>
+        <v>-0.4908</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2613</v>
+        <v>-2.0305</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3016</v>
+        <v>-1.5121</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5629</v>
+        <v>-0.5184</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004</v>
+        <v>0.9913</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6618000000000001</v>
+        <v>1.0706</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6579</v>
+        <v>-0.0793</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2653</v>
+        <v>-3.0219</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3602</v>
+        <v>-2.5827</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.905</v>
+        <v>-0.4391</v>
       </c>
       <c r="P16" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2053</v>
+        <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2635</v>
+        <v>0.6827</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1317</v>
+        <v>0.3755</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3952</v>
+        <v>0.3072</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3095</v>
+        <v>-1.5344</v>
       </c>
       <c r="E17" t="n">
-        <v>0.538</v>
+        <v>0.2242</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8475</v>
+        <v>-1.7586</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5973000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4931</v>
+        <v>0.2683</v>
       </c>
       <c r="T17" t="n">
-        <v>0.368</v>
+        <v>0.0542</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1252</v>
+        <v>0.2141</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5893</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9807</v>
+        <v>-2.181</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5195</v>
+        <v>-2.1367</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4611</v>
+        <v>-0.0443</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0305</v>
+        <v>-4.2292</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5121</v>
+        <v>-3.9479</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5184</v>
+        <v>-0.2813</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9913</v>
+        <v>-1.9308</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0706</v>
+        <v>-2.0886</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0793</v>
+        <v>0.1579</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0219</v>
+        <v>-2.2984</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5827</v>
+        <v>-1.8593</v>
       </c>
       <c r="O18" t="n">
         <v>-0.4391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4641</v>
+        <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0847</v>
+        <v>1.1961</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2521</v>
+        <v>0.9954</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3368</v>
+        <v>0.2007</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>0.8521</v>
       </c>
       <c r="W18" t="n">
+        <v>0.8521</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.8238</v>
+        <v>-4.3578</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6511</v>
+        <v>-2.0522</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1727</v>
+        <v>-2.3056</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.3134</v>
+        <v>-3.8098</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.4</v>
+        <v>-1.1549</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0866</v>
+        <v>-2.6549</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.0779</v>
+        <v>-1.9553</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.8143</v>
+        <v>-0.6</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2636</v>
+        <v>-1.3552</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2355</v>
+        <v>-1.8546</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5857</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3502</v>
+        <v>-1.2997</v>
       </c>
       <c r="P19" t="n">
+        <v>1.6427</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.0267</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>0.311</v>
+        <v>0.1665</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2749</v>
+        <v>-0.097</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0361</v>
+        <v>0.2635</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1786</v>
+        <v>-2.3573</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9739</v>
+        <v>-4.5852</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2301</v>
+        <v>-2.8117</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7438</v>
+        <v>-1.7734</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5831</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.167</v>
+        <v>0.2218</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5928</v>
+        <v>-0.1744</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4259</v>
+        <v>0.3962</v>
       </c>
       <c r="V20" t="n">
         <v>1.4189</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.104</v>
+        <v>-4.6302</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6799</v>
+        <v>-3.5465</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4242</v>
+        <v>-1.0838</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8098</v>
+        <v>-6.3134</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1549</v>
+        <v>-6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6549</v>
+        <v>0.0866</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9553</v>
+        <v>-4.0779</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6</v>
+        <v>-3.8143</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3552</v>
+        <v>-0.2636</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8546</v>
+        <v>-2.2355</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-2.5857</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2997</v>
+        <v>0.3502</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.0267</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.6427</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.5797</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.7246</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.1449</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-2.3573</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3105</v>
+        <v>-5.8625</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5867</v>
+        <v>-4.1683</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7238</v>
+        <v>-1.6942</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7425</v>
@@ -2170,13 +2170,13 @@
         <v>2.2588</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2637</v>
+        <v>0.7118</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0114</v>
+        <v>0.4298</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2523</v>
+        <v>0.282</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6982</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.5639</v>
+        <v>-21.5638</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.338000000000001</v>
+        <v>-8.337900000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-13.2259</v>
@@ -2221,7 +2221,7 @@
         <v>-6.1574</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8496999999999999</v>
+        <v>-0.8497000000000008</v>
       </c>
       <c r="K23" t="n">
         <v>-2.688999999999999</v>
@@ -2248,19 +2248,19 @@
         <v>13.3471</v>
       </c>
       <c r="S23" t="n">
-        <v>5.4038</v>
+        <v>5.404</v>
       </c>
       <c r="T23" t="n">
-        <v>3.0011</v>
+        <v>3.0009</v>
       </c>
       <c r="U23" t="n">
-        <v>2.403</v>
+        <v>2.4031</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3264999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>5.938200000000001</v>
+        <v>5.9382</v>
       </c>
       <c r="X23" t="n">
         <v>-6.2648</v>
